--- a/AAII_Financials/Quarterly/DTEGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DTEGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="92">
   <si>
     <t>DTEGY</t>
   </si>
@@ -656,149 +656,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -841,86 +844,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>32944500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>31259200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>30287300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>30046900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>31000900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>28639100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>55460400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>26938900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>27550200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>27393300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>29499300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22517600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>24938200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>24520600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>23132700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>23311500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>23966700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>21159600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>20167000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>19680600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>21497300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>20477400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>21194400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>21886900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>22939800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>21251800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -963,86 +969,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>15181900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>13326100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12900500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>13187100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>14987700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>11933100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>22936400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>10982800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12633100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>10756800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>11950900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>8957200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11472100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10158800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>9610000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9832800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12222900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9822200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>9203400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>8957500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>11269300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>9368600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>9788200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>10247400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>11877800</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>9909300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1085,86 +1094,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>17762600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>17933100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>17386700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16859800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16013200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>16705900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>32524000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>15956100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>14917100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>16636500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17548400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>13560500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>13466100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>14361800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>13522700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>13478800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>11743800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>11337400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10963500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10723100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>10228100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>11108800</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>11406200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>11639500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>11062000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>11342500</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1207,8 +1219,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1329,8 +1342,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1451,8 +1467,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1495,86 +1514,89 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>532800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>674400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>837800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-2443400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>227200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>207400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>229700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-1141000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>400400</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>215700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>516000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-25700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>169400</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>116000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1032700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>130700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>131800</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>129600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-1868100</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="3">
         <v>-20000</v>
       </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AQ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1617,86 +1639,89 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>6992300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7131500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7621100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7183800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>14758900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>7367100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>14139100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>6927100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>6702500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>7099200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>7568700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4999700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>5363100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5205000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5057300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5026400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>4116500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>3696100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3518000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>3396100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4508200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>4734800</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>3541000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>3745600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>4588400</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>3730400</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1736,8 +1761,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1780,86 +1806,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>28693500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>27843200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>27870600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23326400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>28537800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>25039000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48091400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23346700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>23460800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>24168500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>26131700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>19682500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22846200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>20775800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>20368200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>20610500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>22845300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>18357400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>17584500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>17296800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>20729900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>17001500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>18019200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>18634200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>21839900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>18721100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1902,86 +1931,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>4251000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3416100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2416700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6720500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2463100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3600100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7369000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3592200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4089300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3224800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3367600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2835200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2092000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>3744800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2764500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2701000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1121400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2802200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>2582500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>2383800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>767400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>3475900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>3175200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>3252600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1099900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2530700</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2024,8 +2056,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2068,86 +2101,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>-430900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>448500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>830200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>491500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-195100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-190600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>457100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-381800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>315200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>222100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>313100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-347800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-36200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>82100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>232900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>334900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-291000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>7800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-652200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>86700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-150300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-70700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-390500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-1557600</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-2929800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2190,86 +2226,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>10986300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11453300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11483800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>14552000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9701600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10949900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>22239200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10194700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11339400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11239400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11250600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>7488200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>7720100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9040400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>8116000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>8064800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>5787900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>6512700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>5449400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>5871000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>5125300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>8141200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>6325800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>5440600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2758500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>6447700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2312,86 +2351,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>1628200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>1571300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1527700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1465800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>1366000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>1356900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2652400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>1328100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>1236800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>1250700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>1675600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>741800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>792700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>834200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>782300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>820600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>597400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>562700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>648900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>538000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>657500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>688900</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>678800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>836900</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>728900</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>820500</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2434,86 +2476,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>2191900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2293200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1719200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>5746200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>902000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2052600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5173600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1882400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>3167700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>2196200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>2005100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1745600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1263100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2992700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2215200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2215400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>233000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2247300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1281400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1932500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-40400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2716300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2106000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>858100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-2558900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1896900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2556,86 +2601,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>364400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>310200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>307900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1126200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>79100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>479200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1284400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>553300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>464800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>513800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>564000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>509200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>386400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>764400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>601100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>630400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>469600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>623600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>406300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>542400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-2792600</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1484400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>769700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-91600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>1200</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>462500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2756,8 +2804,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2800,86 +2851,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>1827500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1983100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1411300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4619900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>822800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1573400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3889200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1329100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2703000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1682400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1441100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1236400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>876700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2228300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1614000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-236600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1623700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>875100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>1390100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>2752200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1231900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1336300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>949600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-2560100</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1434400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2922,86 +2976,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>966900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1588600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1483100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4180500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>444500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>907800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>2872500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>955500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>1666700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>848000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>822500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1034300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>763500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1675800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1110500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>1076600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-509800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>543500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>1089200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1494500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>568800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>980600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>876800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-2493200</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1236000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3122,8 +3179,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3166,32 +3226,32 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3">
         <v>156200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>116700</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>105500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>104200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>66100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>49500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>105800</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z29" s="3">
         <v>0</v>
@@ -3244,8 +3304,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3366,8 +3429,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3488,8 +3554,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3532,86 +3601,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>430900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-448500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-830200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-491500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>195100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>190600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-457100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>381800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-315200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-222100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-313100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>347800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>36200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-82100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-232900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-334900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>291000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-7800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>652200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-86700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>150300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>70700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>390500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>1557600</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>2929800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-186600</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3654,86 +3726,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>1123100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1705300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1588600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4284700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>510600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>957400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>2978300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>955500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>1666700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>848000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>822500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1034300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>763500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1675800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1110500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1076600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-509800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>543500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>1089200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>1494500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>568800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>980600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>876800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-2493200</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1236000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3854,8 +3929,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3898,213 +3976,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>1123100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1705300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1588600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4284700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>510600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>957400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>2978300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>955500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>1666700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>848000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>822500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1034300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>763500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1675800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1110500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1076600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-509800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>543500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>1089200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>1494500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>568800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>980600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>876800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-2493200</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1236000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4147,8 +4231,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4191,130 +4276,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6138500</v>
+      </c>
+      <c r="E41" s="3">
         <v>10246700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9179300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6740600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12261900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>18383100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8771100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>13611400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9205000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11680900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8040200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7906400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9543700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11856800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6387500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9182700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5746300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10714400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8257600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6824300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9374900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10077300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>12905400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11045300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15858600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4604500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>6295800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7914700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4580900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7349500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4351900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2475500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3231400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3972600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3716000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3208900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2738800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>11200500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>9093500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>8835300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4322,11 +4411,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>11700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4334,11 +4423,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>6200</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -4346,11 +4435,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>6600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -4358,939 +4447,963 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>5388500</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5387300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4547200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>3880000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>4391700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3558100</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>3238500</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2776600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>3215600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>2750400</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>3028400</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4231900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3798800</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3202100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2572800</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2723700</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>3367700</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3225300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>2838300</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>3204000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>3735100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2739900</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2374100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>5759900</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>6706000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>4923000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23530200</v>
+      </c>
+      <c r="E43" s="3">
         <v>23490100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27402800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22605900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>21287100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20556600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>23090400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>19230400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>19290700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>19344100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24201400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>19470800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20146300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>20222700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21475300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>21015300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>20827300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>19309700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>19138700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>17613800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>17144900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>15924500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>15796800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>15671300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>16189100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14511200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>15413300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>15002500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>14473200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>14817300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>14484600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>12606700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>11989100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>12182300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>11173900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>10497300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>10481600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>10898800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>11245100</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>10226200</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3281200</v>
+      </c>
+      <c r="E44" s="3">
         <v>3333300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3365000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3381400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2741000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2890200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2537500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2832900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2423700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2607600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2673800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2727600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2454100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2889000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2923000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3408500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3255600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3495900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3095100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2302400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2185800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2622400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2688000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2430800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2265800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2137400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1830500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1957500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2002200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2410300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2117400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1706800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1725000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1997300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2227200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1705400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1939900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1932100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1912100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1876900</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11993600</v>
+      </c>
+      <c r="E45" s="3">
         <v>12204500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8387900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12402900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12308900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9856200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4067700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9073200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9155700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8432400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5271400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8273700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8503300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8844000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7181700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6979200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2216500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2210100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7178900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6947100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2682000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>3100200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2590200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2067500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4042900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2087700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1483800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2012700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2017500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2236900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1548400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2116600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>2410100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2477100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2027400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2430200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>2445900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2679800</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2311200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>2182100</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>44943400</v>
+      </c>
+      <c r="E46" s="3">
         <v>49274800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>48346800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>45130800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>48598900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>51686100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38472900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44747900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>40075000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>42064900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>40193400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38378500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>40647400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43812500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>43355900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>45973000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>36592800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>39610100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>42062000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37245700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>34626200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>34501000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>37196000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>33965300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>41384800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>27572600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>28822200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30089400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>25646700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>29537800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>25870000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>22131000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>22193900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>23833200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>22879600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>20581800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>19980400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>32471100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>31268000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>28043500</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12626500</v>
+      </c>
+      <c r="E47" s="3">
         <v>12960900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14233900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13641900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>10606000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8663000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8441900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>6754400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5063800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5075000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6275000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7834500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8022900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7971500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7046600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8711500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7845200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7303100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>6259600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6496900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7364700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6043100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6940900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7465600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7915600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7036600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5235800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6189900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>4006800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3302700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2556200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2431200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2613200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2635200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>7143700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>7364700</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>7879700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>9030100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>10107700</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>10992700</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>106178500</v>
+      </c>
+      <c r="E48" s="3">
         <v>107183200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>103450700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>109293700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>106771600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>103278200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>96050300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>105159500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>104420900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>105682400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>101263400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>106560100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>109336200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>108709300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>110157500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>113115800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>112342000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>108702900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>100330200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>97867600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>96344700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>94405600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>91039700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>96888000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>94617900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>76415200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>78853900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>83857900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>78428200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>78463500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>59891400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>54768600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>52532700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>51140400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>52596600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>51702400</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>51839300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>54920200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>54885000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>52995200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>156298400</v>
+      </c>
+      <c r="E49" s="3">
         <v>156012900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>154943100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>156796900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>153477400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>154187200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>152404000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>151377400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>151763600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>149149900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>147772700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>149288700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>150683400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>150089100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>155728600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>164205900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>157278300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>148888000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>143802600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>140760500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>135880000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>132853000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>117759000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>125454100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>137860500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>77907900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>79619700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>85314400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>77955300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>79412100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>76829400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>71872200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>69872300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>68028800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>70533900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>71332800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>72715000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>70744400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>71131700</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>69197300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5411,8 +5524,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5533,130 +5649,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>7302600</v>
+      </c>
+      <c r="E52" s="3">
         <v>7524500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13487100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>6849700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5869600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5058400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12383300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5285500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6169500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6203500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13726100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6974000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6919200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7541300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14429800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>15284300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>14206200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12773700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12857400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12005300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11977600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11795300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11292600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11573600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>12735300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>7131400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>6712600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>8097200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>7144300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>7221500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6817100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6364300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6232200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5913800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5421500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5918500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>6335900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>7290500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>6900800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>6763500</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5777,130 +5899,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>332850500</v>
+      </c>
+      <c r="E54" s="3">
         <v>338406500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>340224300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>336976400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>330606000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>329636800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>315699300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>321891600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>317201300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>318504700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>320885400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>320187300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>327184500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>330066300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>330718300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>347290500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>328264500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>317277900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>305311800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>294376000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>286193200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>279598100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>264228200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>275346600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>294514100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>196063700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>199244200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>213548800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>193181300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>197937600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>171964100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>157567200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>153444400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>151551500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>158575300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>156900200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>158750400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>174456300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>174293200</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>167992200</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5943,8 +6071,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5987,740 +6116,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10507300</v>
+      </c>
+      <c r="E57" s="3">
         <v>10859000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11150600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>10823700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10463900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9569800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9694600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>8608100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11294300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8991300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11913300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10820300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11336200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12066500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13330000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>12476700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12163900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11788500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11331000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8868300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>8825800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9121900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9734600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>8633300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>10473800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>9857000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>11009800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10897500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>11348700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>12250300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>12698400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>9955100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>9798600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>10026900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>12309400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>9554900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>9800600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>10544300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>12255800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>10438700</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>17748200</v>
+      </c>
+      <c r="E58" s="3">
         <v>18381200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>20044600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21962900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>18233700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>21033300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16074100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>16209000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>15865200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>15467700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>16877400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>15957900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20677900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>19251400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>19743000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>22083000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>17202900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>14976300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>17060500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>14778300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>16000100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>14977200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>16070100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>16436200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>19137800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>13982800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>15191500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>19068200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17773100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16328100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>10193000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6503800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5655800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>8367900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6957500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>7212200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8261200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>13392000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>12643100</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>7976000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15243900</v>
+      </c>
+      <c r="E59" s="3">
         <v>12517000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6915600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12297300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14550800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11381300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6100000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>14027400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13315100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13453400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6161200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>11832100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11235800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>12049100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17199900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18015300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>13773200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12832300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13674800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14082600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12442100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11930100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11233700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11370200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12950200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13281600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>12221600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13214000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12126300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16117600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>11583000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10326200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10298100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10398100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>11437600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>12334000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12456300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>14065800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>13984800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>12116100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>43499400</v>
+      </c>
+      <c r="E60" s="3">
         <v>41757200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43264100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>45083900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43248400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41984400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36424100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>38844500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>40474700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>37912400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>39864000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>38610300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>43250000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>43367000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>50272900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>52575000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43139900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>39597100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>42066300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>37729200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>37268100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>36029100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>37038400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>36439600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>42561900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>37121400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>38423000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>43179700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>41248100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>44696000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>34474400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>26785100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>25752500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>28792900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>30704400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>29101100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>30518100</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>38002100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>38883600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>30530800</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>149915500</v>
+      </c>
+      <c r="E61" s="3">
         <v>153380600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152226100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>148000700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>146540200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>146654800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>141746600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>144135600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>141604000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>143888200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>143746000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>144287700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>145239100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>144628400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>143257000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>150933800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>149540800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>145428000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>136955400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>135064800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>132654200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>130102000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>120829000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>128002100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>133361600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>80729500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>81777100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>86922800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>76707200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>77914500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>60294800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>58453600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>58863800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>52197800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>54214600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>54718300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>56257700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>58640000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>58422900</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>61734200</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6857100</v>
+      </c>
+      <c r="E62" s="3">
         <v>6753100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6334400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6739400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6616600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5878700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5347300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6393000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6243400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6396600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>6235200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5867900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6318800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>6423300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40472800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>41682600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>39295600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37146100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>37969500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>36656600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>34805000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>34371400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>33999400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>36140700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>38406600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>26411900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>25073600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>28153900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>25005600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>24175200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>25813200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>24168900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>23367600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>22588100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>26005500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>29261500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>28672500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>31075400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>31390000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>31567300</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6841,8 +6989,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6963,8 +7114,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7085,130 +7239,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>231418900</v>
+      </c>
+      <c r="E66" s="3">
         <v>232297900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>231932600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>229454400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>225222500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>223955900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>213577000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>218843400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>218160300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>217940400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>220037600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>217975200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>224128800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>222845500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>276935400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>291704700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>276043400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>265056800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>259043500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>250124000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>245597800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>240066600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>228399600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>239107300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>255504200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>160940800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>162229100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>176217300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>159197500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>163246600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>135404200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>123020000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>120920500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>116318800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>124093200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>124142600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>126038700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>139015500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>139894700</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>134612500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7251,8 +7411,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7373,8 +7534,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7495,8 +7659,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7617,8 +7784,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7739,130 +7909,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-3153200</v>
+      </c>
+      <c r="E72" s="3">
         <v>424300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1922000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-3504600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-5566600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-3106400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5953000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-10692600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-12959400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-11359400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13353600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-11416200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-14048000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-11621000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-29338100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-29669500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-31042400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-29796300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-34888500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-35553900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-35339300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-33747600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-34656700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-38309900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-40738900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-39546700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-40674900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-44475700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-43863300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-44998700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-41668800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-38576600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-39690500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-36761000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-39593900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-40982900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-41514800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-41346300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-42318200</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-40349700</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7983,8 +8159,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8105,8 +8284,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8227,130 +8409,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>68824400</v>
+      </c>
+      <c r="E76" s="3">
         <v>72971300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>72996400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>71513600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>69181400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>69259600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>65530600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>65435000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62178300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>63798700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62921400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>65668900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>65111400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>67947600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>53782800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>55585800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>52221200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>52221100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>46268300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>44252000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>40595500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>39531500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>35828600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>36239300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>39009900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>35122900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>37015100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>37331600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>33983800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>34691000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36559900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>34547200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>32523900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>35232600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>34482100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>32757600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>32711600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>35440800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>34398500</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>33379600</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8471,135 +8659,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8642,86 +8836,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>1123100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1705300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1588600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4284700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>510600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>957400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>2978300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>955500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>1666700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>848000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>822500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1034300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>763500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1675800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1110500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1076600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-509800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>543500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>1089200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>1494500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>568800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>980600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>876800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-2493200</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1236000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8764,130 +8961,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6498100</v>
+        <v>6742200</v>
       </c>
       <c r="E83" s="3">
+        <v>6478600</v>
+      </c>
+      <c r="F83" s="3">
         <v>3894800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6502300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6415900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6535800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4374900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6248900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6353700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6496100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6664500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6443400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7943800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6725200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7166200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7588700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8236900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7340000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7433700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>7540500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>14413100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>6984300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>6934900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>7792600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>7569800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5000800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5664300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5213600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5118500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5028800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>4957500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>3702700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>3519100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>3400500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>4508200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>4735900</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>3541000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>3745600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>4588400</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>3730400</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9008,8 +9209,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9130,8 +9334,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9252,8 +9459,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9374,8 +9584,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9496,130 +9709,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11701100</v>
+      </c>
+      <c r="E89" s="3">
         <v>12538900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10521300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12587100</v>
       </c>
-      <c r="G89" s="3">
-        <v>11469200</v>
-      </c>
       <c r="H89" s="3">
+        <v>11470300</v>
+      </c>
+      <c r="I89" s="3">
         <v>12075200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>9494800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>12056700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>11013600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>10372200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>9662900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>10258300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>10159400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>10384600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>9437900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>10042900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>9380500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>10162100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>7103000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10016200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17336400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>8478800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>7206200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>7617100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>5616000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>4470100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6471000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>7258100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6583100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>7189200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>5202400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>5375200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>4823500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>4717000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>4297200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>5394500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>4730300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>5100200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>4162300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>5349100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9662,130 +9881,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3150900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3045100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4088300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3498800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3122700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3449000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2857400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2835200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2738700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3603400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2560000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3170000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3663800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3953700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5906000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5950000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5086000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7172000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5106000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4665000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-6882300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3265500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4201000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3803900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2887600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2725600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2773800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2962000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2812800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3345800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2656800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2600600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2432100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-2558300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-2251800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-2623200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-2531200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-3850100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-3704500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-4560300</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9906,8 +10129,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10028,130 +10254,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5119400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4334100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5424400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12142400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4091600</v>
       </c>
-      <c r="H94" s="3">
-        <v>-5772800</v>
-      </c>
       <c r="I94" s="3">
+        <v>-5771700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4782100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6419800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4173400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4995100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4546300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4050600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4669200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2177300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7526100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5795800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-6132500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4895500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5112600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6870600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17252800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-12630400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-7327900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4201400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9325100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3055300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4662600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3535300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-4415000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4302700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3125200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-6005400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2843800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4000000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3427700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3428800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-8091800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-4097800</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3846600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-5122500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10194,130 +10426,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>6160200</v>
+      </c>
+      <c r="E96" s="3">
         <v>525800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>7559000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>658200</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H96" s="3">
+        <v>5812100</v>
+      </c>
+      <c r="I96" s="3">
         <v>485300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>490700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>552100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>4577300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>378700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>360300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>146100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>3883200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>6500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-149100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-3533100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-62900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-191700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-3077700</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-200300</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-3135300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-186200</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-4010300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-117400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-3456500</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
         <v>0</v>
       </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-62800</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-1685200</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-1200</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-47000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10438,8 +10674,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10560,8 +10799,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10682,370 +10924,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-7102500</v>
+        <v>-10648900</v>
       </c>
       <c r="E100" s="3">
+        <v>-7101300</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2660600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-6010800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-14091600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3345200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9269100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9322800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1674400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-5123200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7757200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7893000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6888300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4356200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1095800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8528500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2878500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-742600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6010200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4774800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>600200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>2892500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-6822100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>15050200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2892800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-3009600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-618600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4805600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>32300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-378500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-160600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2745000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-322800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-350100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1472100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-4431900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1150300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-406100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>159600</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1001800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-420400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>692600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-407100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>86800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>130500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-208900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>203200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-80400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-558900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>294200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>270800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>63300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-579300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>324200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>281800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>61800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>138800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>146500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>376600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>422600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-478800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-636200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>68700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-46700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>42900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>29900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-58200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-12300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-23600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-173900</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-45800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>348600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1232600</v>
+        <v>-4015800</v>
       </c>
       <c r="E102" s="3">
+        <v>1233700</v>
+      </c>
+      <c r="F102" s="3">
         <v>2408100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5484000</v>
       </c>
-      <c r="G102" s="3">
-        <v>-7715800</v>
-      </c>
       <c r="H102" s="3">
-        <v>9227200</v>
+        <v>-7714600</v>
       </c>
       <c r="I102" s="3">
+        <v>9228300</v>
+      </c>
+      <c r="J102" s="3">
         <v>-3863800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4029700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2395800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3833200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-215500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1346300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2399600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5593200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3023700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3475500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4998700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2449900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1386600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2718100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4314500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3128800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2292000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4042600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11409800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1484800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1248000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3147000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2648100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>2948600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1709300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-785300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-741200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>336000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>507100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>470100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-7967300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>2107000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>258200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>375600</v>
       </c>
     </row>
